--- a/docs/downloads/经营分_鲁东省区__青岛北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__青岛北片区_2026-10-18.xlsx
@@ -1307,17 +1307,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7071534219192698887</t>
+          <t>7353864406494611492</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0青岛平度青岛路店）</t>
+          <t>青岛城阳区政府万象汇丽柏酒店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0青岛平度青岛路店)</t>
+          <t>丽柏酒店(青岛城阳区万象汇店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1395,33 +1395,33 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7353864406494611492</t>
+          <t>6694970939702102019</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>青岛城阳区政府万象汇丽柏酒店</t>
+          <t>喆啡酒店（青岛台东步行街营口路店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>丽柏酒店(青岛城阳区万象汇店)</t>
+          <t>喆啡酒店(青岛台东步行街营口路店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,附加分,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1431,25 +1431,25 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
+        <v>25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>30</v>
+      </c>
+      <c r="S10" t="n">
         <v>15</v>
-      </c>
-      <c r="R10" t="n">
-        <v>30</v>
-      </c>
-      <c r="S10" t="n">
-        <v>20</v>
       </c>
       <c r="T10" t="n">
         <v>20</v>
@@ -1483,17 +1483,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6694970939702102019</t>
+          <t>6755293953374865421</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>喆啡酒店（青岛台东步行街营口路店）</t>
+          <t>维也纳国际酒店（青岛流亭机场高铁北站仙家寨地铁站店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>喆啡酒店(青岛台东步行街营口路店)</t>
+          <t>维也纳国际酒店(山东青岛流亭机场高铁北站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1505,11 +1505,11 @@
         <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1519,25 +1519,25 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="n">
         <v>20</v>
@@ -1681,7 +1681,7 @@
         <v>92</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7235885812175341568</t>
+          <t>7071534219192698887</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天酒店（新7天青岛辽阳西路新业广场地铁站店）</t>
+          <t>维也纳酒店（5.0青岛平度青岛路店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天酒店(青岛辽阳西路新业广场地铁站店)</t>
+          <t>维也纳酒店(5.0青岛平度青岛路店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7342388728356145163</t>
+          <t>7235885812175341568</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7天酒店（青岛台东步行街海信桥地铁站店）</t>
+          <t>7天酒店（新7天青岛辽阳西路新业广场地铁站店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7天酒店(青岛台东步行街海信桥地铁站店)</t>
+          <t>7天酒店(青岛辽阳西路新业广场地铁站店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7065165849375541262</t>
+          <t>7342388728356145163</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店青岛啤酒街中山公园店</t>
+          <t>7天酒店（青岛台东步行街海信桥地铁站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(青岛啤酒街中山公园店)</t>
+          <t>7天酒店(青岛台东步行街海信桥地铁站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2004,36 +2004,40 @@
           <t>青岛北片区</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7532426515594610730</t>
+          <t>7065165849375541262</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>潮漫酒店（青岛草原高尔夫流亭地铁站店）</t>
+          <t>希岸Deluxe酒店青岛啤酒街中山公园店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>潮漫酒店(青岛草原高尔夫流亭地铁站店)</t>
+          <t>希岸Deluxe酒店(青岛啤酒街中山公园店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2043,19 +2047,19 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2088,29 +2092,25 @@
           <t>青岛北片区</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6755293953374865421</t>
+          <t>7532426515594610730</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（青岛流亭机场高铁北站仙家寨地铁站店）</t>
+          <t>潮漫酒店（青岛草原高尔夫流亭地铁站店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(山东青岛流亭机场高铁北站店)</t>
+          <t>潮漫酒店(青岛草原高尔夫流亭地铁站店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2131,19 +2131,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30</v>
+      </c>
+      <c r="P18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="n">
         <v>25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30</v>
-      </c>
-      <c r="O18" t="n">
-        <v>25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2447,17 +2447,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7416222055332333602</t>
+          <t>6601133910636103694</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>希岸 Deluxe 酒店(青岛台东步行街啤酒博物馆店）</t>
+          <t>锦江都城酒店（青岛新都心凯德广场地铁站店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(青岛台东步行街啤酒博物馆店)</t>
+          <t>锦江都城酒店(青岛新都心凯德广场店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6601133910636103694</t>
+          <t>7169553531271219236</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>锦江都城酒店（青岛新都心凯德广场地铁站店）</t>
+          <t>麗枫酒店（青岛会展中心览秀城店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>锦江都城酒店(青岛新都心凯德广场店)</t>
+          <t>麗枫酒店(青岛高新会展中心店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7169553531271219236</t>
+          <t>6601154663066634248</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>麗枫酒店（青岛会展中心览秀城店）</t>
+          <t>7天酒店(新7天青岛火车站中山路店)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>麗枫酒店(青岛高新会展中心店)</t>
+          <t>7天酒店(青岛火车站中山路店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2711,17 +2711,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6601154663066634248</t>
+          <t>6601196964027582471</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7天酒店(新7天青岛火车站中山路店)</t>
+          <t>7天酒店（青岛火车北站中心医院地铁站店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7天酒店(青岛火车站中山路店)</t>
+          <t>7天酒店(青岛中心医院地铁站店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2733,7 +2733,7 @@
         <v>105</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2799,17 +2799,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6601196964027582471</t>
+          <t>6601137162224142344</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7天酒店（青岛火车北站中心医院地铁站店）</t>
+          <t>喆啡酒店（青岛黑龙江中路东方城店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7天酒店(青岛中心医院地铁站店)</t>
+          <t>喆·啡酒店(青岛黑龙江中路东方城店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2821,7 +2821,7 @@
         <v>105</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2887,17 +2887,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601137162224142344</t>
+          <t>7416222055332333602</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>喆啡酒店（青岛黑龙江中路东方城店）</t>
+          <t>希岸 Deluxe 酒店(青岛台东步行街啤酒博物馆店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>喆·啡酒店(青岛黑龙江中路东方城店)</t>
+          <t>希岸Deluxe酒店(青岛台东步行街啤酒博物馆店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7249215265789970491</t>
+          <t>7093415612403156992</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（莱西市政府王府井购物中心店）</t>
+          <t>希岸·轻雅酒店（莱西王府井购物中心市政府店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(青岛莱西店)</t>
+          <t>希岸轻雅酒店(青岛莱西市政府店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3151,29 +3151,29 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7093415612403156992</t>
+          <t>7249215265789970491</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店（莱西王府井购物中心市政府店）</t>
+          <t>维也纳智好酒店（莱西市政府王府井购物中心店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>希岸轻雅酒店(青岛莱西市政府店)</t>
+          <t>维也纳智好酒店(青岛莱西店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>110</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
